--- a/Import/Structured_Asset_Base.xlsx
+++ b/Import/Structured_Asset_Base.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$AA$861</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$AA$862</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA861"/>
+  <dimension ref="A1:AA862"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -85508,8 +85508,69 @@
         </is>
       </c>
     </row>
+    <row r="862" ht="20" customHeight="1">
+      <c r="A862" s="2" t="n">
+        <v>111</v>
+      </c>
+      <c r="B862" s="2" t="inlineStr"/>
+      <c r="C862" s="2" t="inlineStr"/>
+      <c r="D862" s="2" t="inlineStr"/>
+      <c r="E862" s="2" t="inlineStr"/>
+      <c r="F862" s="2" t="inlineStr">
+        <is>
+          <t>2222</t>
+        </is>
+      </c>
+      <c r="G862" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H862" s="2" t="inlineStr"/>
+      <c r="I862" s="2" t="inlineStr"/>
+      <c r="J862" s="2" t="inlineStr"/>
+      <c r="K862" s="2" t="inlineStr"/>
+      <c r="L862" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M862" s="2" t="inlineStr"/>
+      <c r="N862" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O862" s="2" t="inlineStr"/>
+      <c r="P862" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q862" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R862" s="2" t="inlineStr"/>
+      <c r="S862" s="2" t="inlineStr"/>
+      <c r="T862" s="2" t="inlineStr"/>
+      <c r="U862" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V862" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W862" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X862" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y862" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z862" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA862" s="2" t="inlineStr">
+        <is>
+          <t>051826a5-b37c-4559-9c8a-148bd876bebb</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AA861"/>
+  <autoFilter ref="A1:AA862"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>